--- a/Result/profitability/3083.xlsx
+++ b/Result/profitability/3083.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.62</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2875</v>
+        <v>0.2775</v>
       </c>
       <c r="N2" t="n">
-        <v>83.62625</v>
+        <v>84.22875000000001</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>1.34</v>
       </c>
       <c r="M3" t="n">
-        <v>0.445</v>
+        <v>0.46125</v>
       </c>
       <c r="N3" t="n">
-        <v>84.2225</v>
+        <v>85.60375000000001</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>2.03</v>
       </c>
       <c r="M4" t="n">
-        <v>0.715</v>
+        <v>0.7</v>
       </c>
       <c r="N4" t="n">
-        <v>86.515</v>
+        <v>87.61375</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>2.87</v>
       </c>
       <c r="M5" t="n">
-        <v>1.05875</v>
+        <v>1.07375</v>
       </c>
       <c r="N5" t="n">
-        <v>88.65625</v>
+        <v>89.18375</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>4.09</v>
       </c>
       <c r="M6" t="n">
-        <v>1.585</v>
+        <v>1.5675</v>
       </c>
       <c r="N6" t="n">
-        <v>90.24625</v>
+        <v>91.22875000000001</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1161,7 +1161,7 @@
         <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
         <v>98.09999999999999</v>
@@ -1264,10 +1264,10 @@
         <v>2.12</v>
       </c>
       <c r="M7" t="n">
-        <v>1.8325</v>
+        <v>1.79625</v>
       </c>
       <c r="N7" t="n">
-        <v>91.5975</v>
+        <v>91.79875</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1288,7 +1288,7 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
         <v>98.2</v>
@@ -1391,10 +1391,10 @@
         <v>3.79</v>
       </c>
       <c r="M8" t="n">
-        <v>2.27</v>
+        <v>2.2325</v>
       </c>
       <c r="N8" t="n">
-        <v>92.22749999999999</v>
+        <v>93.26375</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1415,7 +1415,7 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
         <v>98.3</v>
@@ -1648,7 +1648,7 @@
         <v>2.715</v>
       </c>
       <c r="N10" t="n">
-        <v>94.64</v>
+        <v>94.63999999999999</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -1902,7 +1902,7 @@
         <v>2.89</v>
       </c>
       <c r="N12" t="n">
-        <v>95.52124999999999</v>
+        <v>95.52125000000001</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
@@ -2029,7 +2029,7 @@
         <v>2.83875</v>
       </c>
       <c r="N13" t="n">
-        <v>94.53625</v>
+        <v>94.53625000000001</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3083</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>89</v>
+      </c>
+      <c r="D75" t="n">
+        <v>10</v>
+      </c>
+      <c r="E75" t="n">
+        <v>79</v>
+      </c>
+      <c r="F75" t="n">
+        <v>89.18000000000001</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-0.53%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>3</v>
+      </c>
+      <c r="J75" t="n">
+        <v>2</v>
+      </c>
+      <c r="K75" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.08499999999999999</v>
+      </c>
+      <c r="N75" t="n">
+        <v>83.34999999999999</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>8.290000000000006</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.1024848559772531</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>4.220000000000013</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.04967043314500952</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
